--- a/TPDS/NPB.xlsx
+++ b/TPDS/NPB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimojima/Experimental-Data/TPDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9862E9-59A4-CC45-8BA4-1634C88A2A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660A5C9D-372F-4E40-A9DE-D74DFBA53BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{90F98B5A-A88F-0E44-A2E3-DBA14D0078E0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" activeTab="2" xr2:uid="{90F98B5A-A88F-0E44-A2E3-DBA14D0078E0}"/>
   </bookViews>
   <sheets>
     <sheet name="BT" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="165">
   <si>
     <t>benchmark</t>
   </si>
@@ -539,6 +539,26 @@
     <t>4-&gt;8</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Native+UNENC</t>
+  </si>
+  <si>
+    <t>Native+ENC</t>
+  </si>
+  <si>
+    <t>TEE+UNENC</t>
+  </si>
+  <si>
+    <t>TEE+ENC</t>
+  </si>
+  <si>
+    <t>Native+UNENC (Baseline)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TEE+ENC (Proposal)</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -752,97 +772,13 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Native+UNENC</c:v>
+                  <c:v>Native+UNENC (Baseline)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="3"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>16</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>BT!$D$22:$D$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>4495.8900000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>17511.150000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>39810.89</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3F5E-FC40-BA1A-BB00600D34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>BT!$E$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Native+ENC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4">
                   <a:lumMod val="60000"/>
@@ -855,7 +791,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
@@ -885,7 +821,85 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>16</c:v>
+                <c:v>8</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BT!$D$22:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.4958900000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.511150000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.810890000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3F5E-FC40-BA1A-BB00600D34BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BT!$E$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Native+ENC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="44450" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>8</c:v>
               </c:pt>
             </c:numLit>
           </c:cat>
@@ -896,13 +910,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4494.71</c:v>
+                  <c:v>4.4947100000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17333.650000000001</c:v>
+                  <c:v>17.333650000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38729.1</c:v>
+                  <c:v>38.729099999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -929,7 +943,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2">
                   <a:lumMod val="60000"/>
@@ -942,7 +956,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2">
@@ -972,7 +986,7 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>16</c:v>
+                <c:v>8</c:v>
               </c:pt>
             </c:numLit>
           </c:cat>
@@ -983,13 +997,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3346.9</c:v>
+                  <c:v>3.3469000000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13015.81</c:v>
+                  <c:v>13.01581</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>31589.119999999999</c:v>
+                  <c:v>31.589119999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1010,17 +1024,15 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TEE+ENC</c:v>
+                  <c:v>TEE+ENC (Proposal)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1028,18 +1040,14 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1056,7 +1064,7 @@
                 <c:v>4</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>16</c:v>
+                <c:v>8</c:v>
               </c:pt>
             </c:numLit>
           </c:cat>
@@ -1067,13 +1075,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3358.07</c:v>
+                  <c:v>3.3580700000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12514.79</c:v>
+                  <c:v>12.514790000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30687.3</c:v>
+                  <c:v>30.6873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1112,7 +1120,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1125,10 +1133,10 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>Number of Processes</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of Nodes</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1145,7 +1153,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1183,7 +1191,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1233,7 +1241,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1247,9 +1255,9 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>MFlops</a:t>
+                  <a:t>GFlops</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1266,7 +1274,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1298,7 +1306,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1326,18 +1334,18 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="l"/>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.13543373143793266"/>
-          <c:y val="5.5434440260184875E-2"/>
-          <c:w val="0.2009190468838454"/>
-          <c:h val="0.34047226360218485"/>
+          <c:x val="0.11642658207525196"/>
+          <c:y val="2.5893959247833574E-2"/>
+          <c:w val="0.26464080553877872"/>
+          <c:h val="0.21761468579403689"/>
         </c:manualLayout>
       </c:layout>
-      <c:overlay val="0"/>
+      <c:overlay val="1"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1350,7 +1358,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1392,7 +1400,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="2000"/>
+        <a:defRPr sz="2800" b="1"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -1434,103 +1442,13 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Native+UNENC</c:v>
+                  <c:v>Native+UNENC (Baseline)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>2</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>8</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>CG!$D$30:$D$33</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1183.81</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3092.68</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5335.74</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3432.55</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C9F1-0B4B-A6FF-E7D82DF406B5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>CG!$E$30</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Native+ENC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4">
                   <a:lumMod val="60000"/>
@@ -1543,7 +1461,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
@@ -1582,21 +1500,105 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>CG!$D$30:$D$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.18381</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0926799999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.3357399999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.43255</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F1-0B4B-A6FF-E7D82DF406B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>CG!$E$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Native+ENC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="44450" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>8</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>CG!$H$30:$H$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1167.25</c:v>
+                  <c:v>1.1672499999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3008.37</c:v>
+                  <c:v>3.0083699999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5279.09</c:v>
+                  <c:v>5.2790900000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3388.63</c:v>
+                  <c:v>3.38863</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1623,7 +1625,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2">
                   <a:lumMod val="60000"/>
@@ -1636,7 +1638,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2">
@@ -1680,16 +1682,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1043.96</c:v>
+                  <c:v>1.04396</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2539.4499999999998</c:v>
+                  <c:v>2.53945</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4273.45</c:v>
+                  <c:v>4.2734499999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3210.62</c:v>
+                  <c:v>3.21062</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1710,17 +1712,15 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TEE+ENC</c:v>
+                  <c:v>TEE+ENC (Proposal)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1728,18 +1728,14 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1770,16 +1766,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1035.3399999999999</c:v>
+                  <c:v>1.0353399999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2389.3200000000002</c:v>
+                  <c:v>2.3893200000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3887.71</c:v>
+                  <c:v>3.8877100000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3125.38</c:v>
+                  <c:v>3.1253800000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1818,7 +1814,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1831,14 +1827,9 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>Number</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of Nodes</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-                  <a:t> of Processes</a:t>
-                </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1855,7 +1846,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1893,7 +1884,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1943,7 +1934,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1956,10 +1947,10 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>MFlops</a:t>
+                  <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+                  <a:t>GFlops</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP" b="1"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1976,7 +1967,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2008,7 +1999,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2036,18 +2027,18 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11194246805413773"/>
-          <c:y val="8.1074544591683978E-2"/>
-          <c:w val="0.10935940913114224"/>
-          <c:h val="0.39106035871390493"/>
+          <c:x val="0.10283524252215945"/>
+          <c:y val="2.9575022591443081E-2"/>
+          <c:w val="0.27096682156043156"/>
+          <c:h val="0.20948960222018023"/>
         </c:manualLayout>
       </c:layout>
-      <c:overlay val="0"/>
+      <c:overlay val="1"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2060,7 +2051,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2102,7 +2093,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="2000"/>
+        <a:defRPr sz="2800" b="1"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -2144,13 +2135,13 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Native+UNENC</c:v>
+                  <c:v>Native+UNENC (Baseline)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd" cmpd="sng">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4">
                   <a:lumMod val="60000"/>
@@ -2163,7 +2154,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
@@ -2207,16 +2198,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>136.66</c:v>
+                  <c:v>0.13666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>272.67</c:v>
+                  <c:v>0.27267000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>545.54999999999995</c:v>
+                  <c:v>0.54554999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>965.64</c:v>
+                  <c:v>0.96563999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2243,11 +2234,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2255,18 +2244,14 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent4"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -2297,16 +2282,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>136.4</c:v>
+                  <c:v>0.13639999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>273.04000000000002</c:v>
+                  <c:v>0.27304</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>545.07000000000005</c:v>
+                  <c:v>0.54507000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>964.55</c:v>
+                  <c:v>0.96454999999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2333,7 +2318,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2">
                   <a:lumMod val="60000"/>
@@ -2346,7 +2331,7 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2">
@@ -2390,16 +2375,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>54.23</c:v>
+                  <c:v>5.4229999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108.45</c:v>
+                  <c:v>0.10845</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>216.91</c:v>
+                  <c:v>0.21690999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>383.38</c:v>
+                  <c:v>0.38338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2420,17 +2405,15 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TEE+ENC</c:v>
+                  <c:v>TEE+ENC (Proposal)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="44450" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2438,18 +2421,14 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -2480,16 +2459,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>54.24</c:v>
+                  <c:v>5.4240000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108.46</c:v>
+                  <c:v>0.10845999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>216.82</c:v>
+                  <c:v>0.21681999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>383.47</c:v>
+                  <c:v>0.38347000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2528,7 +2507,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2541,14 +2520,9 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>Number of</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of Nodes</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-                  <a:t> Processes</a:t>
-                </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2565,7 +2539,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2603,7 +2577,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2653,7 +2627,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2667,9 +2641,9 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>MOPS</a:t>
+                  <a:t>GOPS</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2686,7 +2660,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2718,7 +2692,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2746,15 +2720,15 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="l"/>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.17776578827532452"/>
-          <c:y val="0.15864203687763026"/>
-          <c:w val="0.18588976614219005"/>
-          <c:h val="0.25692740057045582"/>
+          <c:x val="0.10001236190153516"/>
+          <c:y val="3.0129702667333603E-2"/>
+          <c:w val="0.26261461871587277"/>
+          <c:h val="0.27215257410850169"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -2770,7 +2744,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2812,7 +2786,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="2000"/>
+        <a:defRPr sz="2800" b="1"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -5740,16 +5714,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>553959</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>209197</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>725965</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>30951</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5774,6 +5748,749 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>776260</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>130119</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>825965</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>130860</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="38" name="グループ化 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622D834C-C642-874A-BB6E-6C972407F6AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="22975860" y="2416119"/>
+          <a:ext cx="4875705" cy="2794741"/>
+          <a:chOff x="18846605" y="6604733"/>
+          <a:chExt cx="4706375" cy="2794741"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="39" name="グループ化 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2858D94-18D2-F9A8-B81F-B2D4D61A76E2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18890767" y="6604733"/>
+            <a:ext cx="4662213" cy="507996"/>
+            <a:chOff x="25887948" y="4318000"/>
+            <a:chExt cx="4699891" cy="508000"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="52" name="テキスト ボックス 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FAE2395-20BF-62CE-0DA5-93DAF1C07528}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26629003" y="4318000"/>
+              <a:ext cx="3958836" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>Native+Unenc (Baseline)</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="53" name="直線コネクタ 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71E7D668-894D-92A8-F3C4-969F4D76E5F2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25887948" y="4594281"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="54" name="円/楕円 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{261B5480-167E-BA84-CB2E-62AD13A7A028}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26128440" y="4521055"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="40" name="グループ化 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3B354F0-852B-38D9-211E-597D1BCC6A09}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18895895" y="7345660"/>
+            <a:ext cx="2641875" cy="507997"/>
+            <a:chOff x="25887948" y="4318000"/>
+            <a:chExt cx="2663992" cy="508000"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="49" name="テキスト ボックス 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DACA2E99-8DBF-6F4D-4692-2D1B1F1F938A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26629003" y="4318000"/>
+              <a:ext cx="1922937" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>Native+Enc </a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="50" name="直線コネクタ 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3801A890-2D6A-7C75-654C-EE9D15CEA8D8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25887948" y="4594281"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="51" name="円/楕円 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89EEC0DA-0047-4F3A-B77A-12F621C0B86C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26136899" y="4521056"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="41" name="グループ化 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1CB9265-0E4E-92D3-7E61-C17E72BF39B6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18898245" y="8133622"/>
+            <a:ext cx="2641875" cy="507995"/>
+            <a:chOff x="25887948" y="4318000"/>
+            <a:chExt cx="2663992" cy="508000"/>
+          </a:xfrm>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="46" name="テキスト ボックス 45">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AE1A479-A331-5EF5-D396-F0C0500DD0B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26629003" y="4318000"/>
+              <a:ext cx="1922937" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>TEE+Unenc </a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="47" name="直線コネクタ 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4529F2-D823-9AD0-9DF9-439EF4C5F83E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25887948" y="4594281"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="48" name="円/楕円 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBBABE6B-6338-617E-5CF8-6EC2138DB663}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26136899" y="4512588"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="42" name="グループ化 41">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23297D10-1311-BBB2-4978-6BDDC64F2685}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="18846605" y="8891478"/>
+            <a:ext cx="3808895" cy="507996"/>
+            <a:chOff x="25901800" y="4289778"/>
+            <a:chExt cx="3839421" cy="508000"/>
+          </a:xfrm>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="43" name="テキスト ボックス 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{161C1955-1864-6B57-CD80-66B06B8BF887}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26670561" y="4289778"/>
+              <a:ext cx="3070660" cy="508000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1">
+                  <a:latin typeface="+mn-lt"/>
+                </a:rPr>
+                <a:t>TEE+Enc (Proposal) </a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1">
+                <a:latin typeface="+mn-lt"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="44" name="直線コネクタ 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{744DAA81-B89F-3A06-B00E-43C474EBAA63}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="25901800" y="4551948"/>
+              <a:ext cx="643912" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln w="34925">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="45" name="円/楕円 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32E7A6A2-3BD7-1BB6-49B6-685DFBC44811}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="26150751" y="4478723"/>
+              <a:ext cx="134453" cy="155465"/>
+            </a:xfrm>
+            <a:prstGeom prst="ellipse">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:grpFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" rtlCol="0" anchor="t" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5781,16 +6498,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>257681</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352084</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>179903</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>349710</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>36813</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>444671</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>229064</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5822,16 +6539,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>444102</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>209431</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>455912</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>145377</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>411154</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>78836</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>631687</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>16537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6278,7 +6995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D4117D1-A542-8241-AD58-531253AA4DDC}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -6933,7 +7650,7 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>26</v>
@@ -6942,7 +7659,8 @@
         <v>1</v>
       </c>
       <c r="D22" s="4">
-        <v>4495.8900000000003</v>
+        <f>4495.89/1000</f>
+        <v>4.4958900000000002</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>154</v>
@@ -6954,7 +7672,8 @@
         <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>4494.71</v>
+        <f>4494.71/1000</f>
+        <v>4.4947100000000004</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>153</v>
@@ -6966,10 +7685,11 @@
         <v>1</v>
       </c>
       <c r="L22" s="4">
-        <v>3346.9</v>
+        <f>3346.9/1000</f>
+        <v>3.3469000000000002</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>18</v>
@@ -6978,7 +7698,8 @@
         <v>1</v>
       </c>
       <c r="P22" s="3">
-        <v>3358.07</v>
+        <f>3358.07/1000</f>
+        <v>3.3580700000000001</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -6992,7 +7713,8 @@
         <v>4</v>
       </c>
       <c r="D23" s="3">
-        <v>17511.150000000001</v>
+        <f>17511.15/1000</f>
+        <v>17.511150000000001</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>154</v>
@@ -7004,7 +7726,8 @@
         <v>4</v>
       </c>
       <c r="H23" s="4">
-        <v>17333.650000000001</v>
+        <f>17333.65/1000</f>
+        <v>17.333650000000002</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>153</v>
@@ -7016,7 +7739,8 @@
         <v>4</v>
       </c>
       <c r="L23" s="3">
-        <v>13015.81</v>
+        <f>13015.81/1000</f>
+        <v>13.01581</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>152</v>
@@ -7028,7 +7752,8 @@
         <v>4</v>
       </c>
       <c r="P23" s="4">
-        <v>12514.79</v>
+        <f>12514.79/1000</f>
+        <v>12.514790000000001</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -7042,7 +7767,8 @@
         <v>16</v>
       </c>
       <c r="D24" s="4">
-        <v>39810.89</v>
+        <f>39810.89/1000</f>
+        <v>39.810890000000001</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>154</v>
@@ -7054,7 +7780,8 @@
         <v>16</v>
       </c>
       <c r="H24" s="3">
-        <v>38729.1</v>
+        <f>38729.1/1000</f>
+        <v>38.729099999999995</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>153</v>
@@ -7066,7 +7793,8 @@
         <v>16</v>
       </c>
       <c r="L24" s="4">
-        <v>31589.119999999999</v>
+        <f>31589.12/1000</f>
+        <v>31.589119999999998</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>152</v>
@@ -7078,17 +7806,18 @@
         <v>16</v>
       </c>
       <c r="P24" s="3">
-        <v>30687.3</v>
+        <f>30687.3/1000</f>
+        <v>30.6873</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="D25">
         <f>D24/D22</f>
-        <v>8.85495196724119</v>
+        <v>8.8549519672411918</v>
       </c>
       <c r="H25">
         <f>H24/H22</f>
-        <v>8.616595953910263</v>
+        <v>8.6165959539102612</v>
       </c>
       <c r="L25">
         <f>L24/L22</f>
@@ -7096,7 +7825,7 @@
       </c>
       <c r="P25">
         <f>P24/P22</f>
-        <v>9.1383741256138187</v>
+        <v>9.1383741256138205</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -7109,6 +7838,168 @@
       <c r="L28">
         <f>L24/L23</f>
         <v>2.4269807257481477</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <f>D22/P22</f>
+        <v>1.3388315312069134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <f>H22/P22</f>
+        <v>1.3384801388893026</v>
+      </c>
+      <c r="I29" t="s">
+        <v>161</v>
+      </c>
+      <c r="J29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <f>L22/P22</f>
+        <v>0.99667368458668226</v>
+      </c>
+      <c r="M29" t="s">
+        <v>162</v>
+      </c>
+      <c r="N29" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <f>P22/P22</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <f>D23/P22</f>
+        <v>5.2146471038423856</v>
+      </c>
+      <c r="E30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <f>H23/P22</f>
+        <v>5.1617893611509</v>
+      </c>
+      <c r="I30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J30" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <f>L23/P22</f>
+        <v>3.8759793571902907</v>
+      </c>
+      <c r="M30" t="s">
+        <v>162</v>
+      </c>
+      <c r="N30" t="s">
+        <v>18</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
+      <c r="P30">
+        <f>P23/P22</f>
+        <v>3.7267805614534542</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <f>D24/P22</f>
+        <v>11.855288901065196</v>
+      </c>
+      <c r="E31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31">
+        <v>16</v>
+      </c>
+      <c r="H31">
+        <f>H24/P22</f>
+        <v>11.533142549142809</v>
+      </c>
+      <c r="I31" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31">
+        <v>16</v>
+      </c>
+      <c r="L31">
+        <f>L24/P22</f>
+        <v>9.4069271932985306</v>
+      </c>
+      <c r="M31" t="s">
+        <v>162</v>
+      </c>
+      <c r="N31" t="s">
+        <v>18</v>
+      </c>
+      <c r="O31">
+        <v>16</v>
+      </c>
+      <c r="P31">
+        <f>P24/P22</f>
+        <v>9.1383741256138205</v>
       </c>
     </row>
   </sheetData>
@@ -7120,7 +8011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AD0989-BE0A-C04C-AD97-E4555100D427}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -7975,7 +8866,7 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>26</v>
@@ -7984,7 +8875,8 @@
         <v>1</v>
       </c>
       <c r="D30" s="3">
-        <v>1183.81</v>
+        <f>1183.81/1000</f>
+        <v>1.18381</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>154</v>
@@ -7996,7 +8888,8 @@
         <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>1167.25</v>
+        <f>1167.25/1000</f>
+        <v>1.1672499999999999</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>153</v>
@@ -8008,10 +8901,11 @@
         <v>1</v>
       </c>
       <c r="L30" s="3">
-        <v>1043.96</v>
+        <f>1043.96/1000</f>
+        <v>1.04396</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>18</v>
@@ -8020,7 +8914,8 @@
         <v>1</v>
       </c>
       <c r="P30" s="3">
-        <v>1035.3399999999999</v>
+        <f>1035.34/1000</f>
+        <v>1.0353399999999999</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -8034,7 +8929,8 @@
         <v>2</v>
       </c>
       <c r="D31" s="4">
-        <v>3092.68</v>
+        <f>3092.68/1000</f>
+        <v>3.0926799999999997</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>154</v>
@@ -8046,7 +8942,8 @@
         <v>2</v>
       </c>
       <c r="H31" s="4">
-        <v>3008.37</v>
+        <f>3008.37/1000</f>
+        <v>3.0083699999999998</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>153</v>
@@ -8058,7 +8955,8 @@
         <v>2</v>
       </c>
       <c r="L31" s="4">
-        <v>2539.4499999999998</v>
+        <f>2539.45/1000</f>
+        <v>2.53945</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>152</v>
@@ -8070,7 +8968,8 @@
         <v>2</v>
       </c>
       <c r="P31" s="4">
-        <v>2389.3200000000002</v>
+        <f>2389.32/1000</f>
+        <v>2.3893200000000001</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -8084,7 +8983,8 @@
         <v>4</v>
       </c>
       <c r="D32" s="3">
-        <v>5335.74</v>
+        <f>5335.74/1000</f>
+        <v>5.3357399999999995</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>154</v>
@@ -8096,7 +8996,8 @@
         <v>4</v>
       </c>
       <c r="H32" s="3">
-        <v>5279.09</v>
+        <f>5279.09/1000</f>
+        <v>5.2790900000000001</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>153</v>
@@ -8108,7 +9009,8 @@
         <v>4</v>
       </c>
       <c r="L32" s="3">
-        <v>4273.45</v>
+        <f>4273.45/1000</f>
+        <v>4.2734499999999995</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>152</v>
@@ -8120,7 +9022,8 @@
         <v>4</v>
       </c>
       <c r="P32" s="3">
-        <v>3887.71</v>
+        <f>3887.71/1000</f>
+        <v>3.8877100000000002</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -8134,7 +9037,8 @@
         <v>8</v>
       </c>
       <c r="D33" s="4">
-        <v>3432.55</v>
+        <f>3432.55/1000</f>
+        <v>3.43255</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>154</v>
@@ -8146,7 +9050,8 @@
         <v>8</v>
       </c>
       <c r="H33" s="4">
-        <v>3388.63</v>
+        <f>3388.63/1000</f>
+        <v>3.38863</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>153</v>
@@ -8158,7 +9063,8 @@
         <v>8</v>
       </c>
       <c r="L33" s="4">
-        <v>3210.62</v>
+        <f>3210.62/1000</f>
+        <v>3.21062</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>152</v>
@@ -8170,7 +9076,8 @@
         <v>8</v>
       </c>
       <c r="P33" s="4">
-        <v>3125.38</v>
+        <f>3125.38/1000</f>
+        <v>3.1253800000000003</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -8179,15 +9086,15 @@
       </c>
       <c r="D34">
         <f>D32/D30</f>
-        <v>4.5072604556474438</v>
+        <v>4.5072604556474429</v>
       </c>
       <c r="H34">
         <f>H32/H30</f>
-        <v>4.5226729492396656</v>
+        <v>4.5226729492396665</v>
       </c>
       <c r="L34">
         <f>L31/L30</f>
-        <v>2.4325165715161496</v>
+        <v>2.4325165715161501</v>
       </c>
       <c r="P34">
         <f>P31/P30</f>
@@ -8213,6 +9120,222 @@
       <c r="P35">
         <f>P33/P32</f>
         <v>0.80391284329335266</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <f>D30/P30</f>
+        <v>1.1434021674039447</v>
+      </c>
+      <c r="E37" t="s">
+        <v>160</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <f>H30/P30</f>
+        <v>1.1274074217165375</v>
+      </c>
+      <c r="I37" t="s">
+        <v>161</v>
+      </c>
+      <c r="J37" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <f>L30/P30</f>
+        <v>1.008325767380764</v>
+      </c>
+      <c r="M37" t="s">
+        <v>162</v>
+      </c>
+      <c r="N37" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <f>P30/P30</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <f>D31/P30</f>
+        <v>2.9871153437518108</v>
+      </c>
+      <c r="E38" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <f>H31/P30</f>
+        <v>2.9056831572237138</v>
+      </c>
+      <c r="I38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J38" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38">
+        <f>L31/P30</f>
+        <v>2.4527691386404467</v>
+      </c>
+      <c r="M38" t="s">
+        <v>162</v>
+      </c>
+      <c r="N38" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38">
+        <v>2</v>
+      </c>
+      <c r="P38">
+        <f>P31/P30</f>
+        <v>2.3077636332026197</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39">
+        <f>D32/P30</f>
+        <v>5.1536113740413771</v>
+      </c>
+      <c r="E39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <f>H32/P30</f>
+        <v>5.0988950489694211</v>
+      </c>
+      <c r="I39" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="L39">
+        <f>L32/P30</f>
+        <v>4.1275812776479226</v>
+      </c>
+      <c r="M39" t="s">
+        <v>162</v>
+      </c>
+      <c r="N39" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39">
+        <v>4</v>
+      </c>
+      <c r="P39">
+        <f>P32/P30</f>
+        <v>3.7550080166901698</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <f>D33/P30</f>
+        <v>3.3153843181949894</v>
+      </c>
+      <c r="E40" t="s">
+        <v>160</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40">
+        <v>8</v>
+      </c>
+      <c r="H40">
+        <f>H33/P30</f>
+        <v>3.2729634709370838</v>
+      </c>
+      <c r="I40" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40">
+        <v>8</v>
+      </c>
+      <c r="L40">
+        <f>L33/P30</f>
+        <v>3.1010296134603128</v>
+      </c>
+      <c r="M40" t="s">
+        <v>162</v>
+      </c>
+      <c r="N40" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40">
+        <v>8</v>
+      </c>
+      <c r="P40">
+        <f>P33/P30</f>
+        <v>3.0186991712867277</v>
       </c>
     </row>
   </sheetData>
@@ -8224,7 +9347,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA785BCF-C4AD-1144-9611-514C68116144}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -9067,7 +10190,7 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>26</v>
@@ -9076,7 +10199,8 @@
         <v>1</v>
       </c>
       <c r="D26" s="3">
-        <v>136.66</v>
+        <f>136.66/1000</f>
+        <v>0.13666</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>154</v>
@@ -9088,7 +10212,8 @@
         <v>1</v>
       </c>
       <c r="H26" s="3">
-        <v>136.4</v>
+        <f>136.4/1000</f>
+        <v>0.13639999999999999</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>153</v>
@@ -9100,10 +10225,11 @@
         <v>1</v>
       </c>
       <c r="L26" s="3">
-        <v>54.23</v>
+        <f>54.23/1000</f>
+        <v>5.4229999999999993E-2</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>18</v>
@@ -9112,7 +10238,8 @@
         <v>1</v>
       </c>
       <c r="P26" s="3">
-        <v>54.24</v>
+        <f>54.24/1000</f>
+        <v>5.4240000000000003E-2</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -9126,7 +10253,8 @@
         <v>2</v>
       </c>
       <c r="D27" s="4">
-        <v>272.67</v>
+        <f>272.67/1000</f>
+        <v>0.27267000000000002</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>154</v>
@@ -9138,7 +10266,8 @@
         <v>2</v>
       </c>
       <c r="H27" s="4">
-        <v>273.04000000000002</v>
+        <f>273.04/1000</f>
+        <v>0.27304</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>153</v>
@@ -9150,7 +10279,8 @@
         <v>2</v>
       </c>
       <c r="L27" s="4">
-        <v>108.45</v>
+        <f>108.45/1000</f>
+        <v>0.10845</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>152</v>
@@ -9162,7 +10292,8 @@
         <v>2</v>
       </c>
       <c r="P27" s="4">
-        <v>108.46</v>
+        <f>108.46/1000</f>
+        <v>0.10845999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -9176,7 +10307,8 @@
         <v>4</v>
       </c>
       <c r="D28" s="3">
-        <v>545.54999999999995</v>
+        <f>545.55/1000</f>
+        <v>0.54554999999999998</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>154</v>
@@ -9188,7 +10320,8 @@
         <v>4</v>
       </c>
       <c r="H28" s="10">
-        <v>545.07000000000005</v>
+        <f>545.07/1000</f>
+        <v>0.54507000000000005</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>153</v>
@@ -9200,7 +10333,8 @@
         <v>4</v>
       </c>
       <c r="L28" s="3">
-        <v>216.91</v>
+        <f>216.91/1000</f>
+        <v>0.21690999999999999</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>152</v>
@@ -9212,7 +10346,8 @@
         <v>4</v>
       </c>
       <c r="P28" s="3">
-        <v>216.82</v>
+        <f>216.82/1000</f>
+        <v>0.21681999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -9226,7 +10361,8 @@
         <v>8</v>
       </c>
       <c r="D29" s="4">
-        <v>965.64</v>
+        <f>965.64/1000</f>
+        <v>0.96563999999999994</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>154</v>
@@ -9238,7 +10374,8 @@
         <v>8</v>
       </c>
       <c r="H29" s="4">
-        <v>964.55</v>
+        <f>964.55/1000</f>
+        <v>0.96454999999999991</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>153</v>
@@ -9250,7 +10387,8 @@
         <v>8</v>
       </c>
       <c r="L29" s="4">
-        <v>383.38</v>
+        <f>383.38/1000</f>
+        <v>0.38338</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>152</v>
@@ -9262,7 +10400,8 @@
         <v>8</v>
       </c>
       <c r="P29" s="4">
-        <v>383.47</v>
+        <f>383.47/1000</f>
+        <v>0.38347000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -9272,13 +10411,229 @@
       </c>
       <c r="H30">
         <f>H29/H26</f>
-        <v>7.0714809384164212</v>
+        <v>7.0714809384164221</v>
       </c>
       <c r="L30">
         <f>L29/L26</f>
         <v>7.0695187165775408</v>
       </c>
       <c r="P30">
+        <f>P29/P26</f>
+        <v>7.0698746312684371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <f>D26/P26</f>
+        <v>2.5195427728613566</v>
+      </c>
+      <c r="E32" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <f>H26/P26</f>
+        <v>2.5147492625368728</v>
+      </c>
+      <c r="I32" t="s">
+        <v>161</v>
+      </c>
+      <c r="J32" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <f>L26/P26</f>
+        <v>0.9998156342182889</v>
+      </c>
+      <c r="M32" t="s">
+        <v>162</v>
+      </c>
+      <c r="N32" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32">
+        <f>P26/P26</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <f>D27/P26</f>
+        <v>5.0271017699115044</v>
+      </c>
+      <c r="E33" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <f>H27/P26</f>
+        <v>5.0339233038348077</v>
+      </c>
+      <c r="I33" t="s">
+        <v>161</v>
+      </c>
+      <c r="J33" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <f>L27/P26</f>
+        <v>1.9994469026548671</v>
+      </c>
+      <c r="M33" t="s">
+        <v>162</v>
+      </c>
+      <c r="N33" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33">
+        <v>2</v>
+      </c>
+      <c r="P33">
+        <f>P27/P26</f>
+        <v>1.9996312684365778</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <f>D28/P26</f>
+        <v>10.058075221238937</v>
+      </c>
+      <c r="E34" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <f>H28/P26</f>
+        <v>10.049225663716815</v>
+      </c>
+      <c r="I34" t="s">
+        <v>161</v>
+      </c>
+      <c r="J34" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <f>L28/P26</f>
+        <v>3.9990781710914449</v>
+      </c>
+      <c r="M34" t="s">
+        <v>162</v>
+      </c>
+      <c r="N34" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="P34">
+        <f>P28/P26</f>
+        <v>3.9974188790560468</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <f>D29/P26</f>
+        <v>17.803097345132741</v>
+      </c>
+      <c r="E35" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+      <c r="H35">
+        <f>H29/P26</f>
+        <v>17.783001474926252</v>
+      </c>
+      <c r="I35" t="s">
+        <v>161</v>
+      </c>
+      <c r="J35" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35">
+        <v>8</v>
+      </c>
+      <c r="L35">
+        <f>L29/P26</f>
+        <v>7.0682153392330376</v>
+      </c>
+      <c r="M35" t="s">
+        <v>162</v>
+      </c>
+      <c r="N35" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35">
+        <v>8</v>
+      </c>
+      <c r="P35">
         <f>P29/P26</f>
         <v>7.0698746312684371</v>
       </c>
